--- a/data/trans_dic/P16A09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,93</t>
+          <t>1,33; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,86</t>
+          <t>0,69; 4,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,2</t>
+          <t>0,68; 4,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,87</t>
+          <t>2,39; 8,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,77</t>
+          <t>1,85; 6,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,18</t>
+          <t>1,96; 6,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,15</t>
+          <t>2,03; 4,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,47</t>
+          <t>2,41; 5,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,73</t>
+          <t>1,56; 4,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,64</t>
+          <t>1,65; 4,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,57</t>
+          <t>1,01; 2,66</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,43</t>
+          <t>0,41; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,68</t>
+          <t>1,47; 5,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,77</t>
+          <t>0,58; 2,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,89</t>
+          <t>0,17; 1,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,97</t>
+          <t>3,88; 7,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,66</t>
+          <t>3,45; 7,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,81</t>
+          <t>1,7; 4,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,07</t>
+          <t>1,04; 3,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,66</t>
+          <t>2,37; 4,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,51</t>
+          <t>2,83; 5,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,19</t>
+          <t>1,44; 3,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,04</t>
+          <t>0,73; 1,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,01</t>
+          <t>0,31; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,21</t>
+          <t>0,62; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,22</t>
+          <t>1,05; 4,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,54</t>
+          <t>0,83; 3,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,45</t>
+          <t>0,95; 4,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,43</t>
+          <t>3,35; 8,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,66</t>
+          <t>1,72; 5,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,66</t>
+          <t>3,1; 6,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,04</t>
+          <t>0,89; 3,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,47</t>
+          <t>2,45; 5,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,38</t>
+          <t>1,69; 4,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,43</t>
+          <t>2,3; 4,58</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,16</t>
+          <t>0,82; 3,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,67</t>
+          <t>1,77; 5,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,48</t>
+          <t>0,69; 3,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,16</t>
+          <t>1,62; 5,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,52</t>
+          <t>2,46; 6,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,16</t>
+          <t>5,16; 10,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,53</t>
+          <t>2,46; 6,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,04</t>
+          <t>1,93; 6,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,52</t>
+          <t>2,01; 4,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,16</t>
+          <t>3,78; 7,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,31</t>
+          <t>1,8; 4,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,39</t>
+          <t>2,42; 5,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,07</t>
+          <t>2,01; 8,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,54</t>
+          <t>1,62; 7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 15,55</t>
+          <t>6,49; 15,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 14,31</t>
+          <t>6,37; 14,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,26</t>
+          <t>2,94; 10,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,32</t>
+          <t>2,33; 5,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,56</t>
+          <t>4,82; 10,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,55</t>
+          <t>4,84; 10,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,23</t>
+          <t>1,54; 5,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,3</t>
+          <t>1,43; 3,26</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,27</t>
+          <t>0,73; 4,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,61</t>
+          <t>1,1; 4,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,67</t>
+          <t>0,73; 4,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,17</t>
+          <t>1,4; 4,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,49</t>
+          <t>1,83; 6,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,39</t>
+          <t>3,63; 9,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,9</t>
+          <t>2,74; 8,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,87</t>
+          <t>3,91; 7,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,68</t>
+          <t>1,75; 4,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,03</t>
+          <t>2,45; 5,97</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,33</t>
+          <t>2,04; 5,31</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,24</t>
+          <t>2,97; 5,59</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,92</t>
+          <t>2,66; 6,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,36</t>
+          <t>0,6; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,7</t>
+          <t>0,75; 2,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,35</t>
+          <t>1,28; 3,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,53</t>
+          <t>2,51; 5,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,67</t>
+          <t>3,32; 6,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,03</t>
+          <t>2,14; 5,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,89</t>
+          <t>1,63; 5,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,18</t>
+          <t>3,02; 5,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,1</t>
+          <t>2,14; 4,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,57</t>
+          <t>1,72; 3,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,9</t>
+          <t>1,75; 3,78</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,78</t>
+          <t>3,02; 5,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,48</t>
+          <t>0,68; 2,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,52</t>
+          <t>0,11; 1,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,14</t>
+          <t>0,73; 3,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,55</t>
+          <t>5,02; 8,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,95</t>
+          <t>4,54; 7,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,29</t>
+          <t>2,5; 5,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,29</t>
+          <t>9,82; 14,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,73</t>
+          <t>4,34; 6,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,81</t>
+          <t>2,94; 4,86</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,02</t>
+          <t>1,46; 3,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,78</t>
+          <t>3,66; 7,68</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,54</t>
+          <t>2,39; 3,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,67</t>
+          <t>1,6; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,79</t>
+          <t>0,98; 1,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,29</t>
+          <t>1,31; 2,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,9</t>
+          <t>4,33; 5,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,63</t>
+          <t>5,0; 6,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,88</t>
+          <t>4,2; 5,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,48</t>
+          <t>3,55; 4,53</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,01</t>
+          <t>2,2; 3,02</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,92</t>
+          <t>2,99; 3,98</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el reuma en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3607; 13452</t>
+          <t>3642; 15327</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1993; 14115</t>
+          <t>1990; 13443</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2022; 12325</t>
+          <t>1988; 12107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 3501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6202; 20535</t>
+          <t>6244; 21321</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5204; 18987</t>
+          <t>5178; 19089</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5476; 20734</t>
+          <t>5668; 19051</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5708; 14910</t>
+          <t>5881; 14354</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12737; 29204</t>
+          <t>12854; 31016</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9135; 26973</t>
+          <t>8919; 27462</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10289; 27009</t>
+          <t>9629; 27288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5951; 15444</t>
+          <t>6060; 16003</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1949; 11970</t>
+          <t>2035; 11335</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7388; 28701</t>
+          <t>7434; 26726</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3114; 13932</t>
+          <t>2891; 13881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>907; 9755</t>
+          <t>868; 9312</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19730; 40160</t>
+          <t>19562; 40162</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19047; 40049</t>
+          <t>18057; 37320</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8746; 25143</t>
+          <t>8886; 24401</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5213; 15758</t>
+          <t>5336; 15765</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24175; 46473</t>
+          <t>23620; 46728</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28570; 56672</t>
+          <t>29148; 56185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13907; 32750</t>
+          <t>14789; 34514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7993; 21050</t>
+          <t>7496; 20378</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>958; 9612</t>
+          <t>993; 10605</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2008; 10377</t>
+          <t>1991; 11102</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3806; 13447</t>
+          <t>3348; 13270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2857; 11185</t>
+          <t>2622; 10538</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3758; 14912</t>
+          <t>3182; 14474</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13577; 32143</t>
+          <t>11433; 30405</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5777; 19048</t>
+          <t>5777; 19630</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10422; 23246</t>
+          <t>10828; 22619</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6325; 19919</t>
+          <t>5829; 19646</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16538; 36309</t>
+          <t>16293; 36782</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11209; 28678</t>
+          <t>11087; 27690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14965; 29448</t>
+          <t>15304; 30425</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2876; 14935</t>
+          <t>2926; 13644</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6415; 21209</t>
+          <t>6618; 20724</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2017; 12857</t>
+          <t>2538; 14209</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5357; 19250</t>
+          <t>5076; 18596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9234; 24235</t>
+          <t>9148; 24547</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19158; 39294</t>
+          <t>19967; 40321</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9322; 25308</t>
+          <t>9539; 25809</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9821; 28706</t>
+          <t>9181; 28652</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14320; 32972</t>
+          <t>14642; 33412</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30071; 54474</t>
+          <t>28765; 55354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13491; 32654</t>
+          <t>13621; 33182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19030; 42469</t>
+          <t>19043; 41039</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3822; 16411</t>
+          <t>4082; 17205</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3378; 16040</t>
+          <t>3444; 15789</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3731</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12848; 32297</t>
+          <t>13481; 31703</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13161; 31430</t>
+          <t>13998; 32540</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6542; 22431</t>
+          <t>6426; 21953</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4666; 11106</t>
+          <t>4855; 11684</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19843; 43384</t>
+          <t>19823; 42914</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20182; 41293</t>
+          <t>20926; 43337</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6988; 22470</t>
+          <t>6598; 22082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5646; 12770</t>
+          <t>5554; 12627</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2721; 11574</t>
+          <t>1984; 11350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2145; 12619</t>
+          <t>3023; 12706</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2014; 12298</t>
+          <t>1924; 11522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3769; 11256</t>
+          <t>3785; 11422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4967; 18039</t>
+          <t>5083; 18229</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9212; 26206</t>
+          <t>10141; 25891</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7778; 21580</t>
+          <t>7484; 22161</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9793; 20228</t>
+          <t>10039; 20034</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10074; 25666</t>
+          <t>9603; 25015</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14917; 33352</t>
+          <t>13537; 33011</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11339; 28579</t>
+          <t>10956; 28484</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15086; 27588</t>
+          <t>15663; 29463</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17032; 36395</t>
+          <t>16381; 37317</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3955; 15643</t>
+          <t>3974; 16856</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4808; 17708</t>
+          <t>4924; 17011</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8125; 20861</t>
+          <t>7962; 21220</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16391; 35297</t>
+          <t>16037; 35428</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22283; 46289</t>
+          <t>23044; 46026</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14603; 34794</t>
+          <t>14782; 36252</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12778; 41563</t>
+          <t>13829; 42747</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37709; 64967</t>
+          <t>37853; 65183</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29039; 55642</t>
+          <t>29056; 56226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22102; 48184</t>
+          <t>23185; 46949</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27017; 57375</t>
+          <t>25752; 55638</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22242; 42930</t>
+          <t>22458; 43582</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5317; 19282</t>
+          <t>5300; 18296</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>819; 11833</t>
+          <t>858; 13198</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6806; 29150</t>
+          <t>6762; 29013</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>39500; 67022</t>
+          <t>39348; 69180</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36132; 65275</t>
+          <t>37324; 65205</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20818; 43729</t>
+          <t>20647; 44255</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>69377; 102137</t>
+          <t>70215; 103694</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>67558; 102650</t>
+          <t>66258; 102548</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43709; 76847</t>
+          <t>46988; 77709</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22807; 48408</t>
+          <t>23474; 50069</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>60819; 127937</t>
+          <t>60170; 126196</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>77076; 115878</t>
+          <t>78300; 114764</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>55242; 91401</t>
+          <t>54702; 90999</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34225; 60827</t>
+          <t>33114; 59638</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45805; 79269</t>
+          <t>45136; 78273</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>147850; 199364</t>
+          <t>146473; 198455</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>181182; 235216</t>
+          <t>177098; 236451</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>110223; 158235</t>
+          <t>111719; 159042</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>152825; 215091</t>
+          <t>153628; 214832</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>235279; 298426</t>
+          <t>236178; 301417</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>245081; 315223</t>
+          <t>246216; 313136</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>154896; 209063</t>
+          <t>152690; 209726</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>211225; 278841</t>
+          <t>212623; 282968</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A09-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,61</t>
+          <t>1,37; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,63</t>
+          <t>0,68; 4,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,12</t>
+          <t>0,69; 4,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,17</t>
+          <t>2,49; 7,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,81</t>
+          <t>1,82; 7,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,6</t>
+          <t>2,0; 7,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,96</t>
+          <t>1,9; 4,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,81</t>
+          <t>2,33; 5,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,81</t>
+          <t>1,56; 4,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,68</t>
+          <t>1,69; 4,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,66</t>
+          <t>1,03; 2,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,3</t>
+          <t>0,39; 2,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,29</t>
+          <t>1,47; 5,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,76</t>
+          <t>0,6; 2,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,17; 1,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,97</t>
+          <t>4,03; 7,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,14</t>
+          <t>3,42; 7,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,66</t>
+          <t>1,7; 4,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,07</t>
+          <t>1,03; 2,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,69</t>
+          <t>2,42; 4,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,46</t>
+          <t>2,9; 5,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,37</t>
+          <t>1,4; 3,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,98</t>
+          <t>0,71; 2,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,33</t>
+          <t>0,3; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,44</t>
+          <t>0,62; 3,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,17</t>
+          <t>1,04; 3,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,34</t>
+          <t>0,83; 3,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,32</t>
+          <t>1,12; 4,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,92</t>
+          <t>3,76; 9,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,84</t>
+          <t>1,76; 5,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,48</t>
+          <t>3,04; 6,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,0</t>
+          <t>0,92; 3,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,54</t>
+          <t>2,45; 5,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,23</t>
+          <t>1,67; 4,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,58</t>
+          <t>2,27; 4,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,8</t>
+          <t>0,81; 3,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,54</t>
+          <t>1,76; 5,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,84</t>
+          <t>0,67; 3,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,95</t>
+          <t>1,43; 5,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,61</t>
+          <t>2,5; 6,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,42</t>
+          <t>5,14; 10,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,66</t>
+          <t>2,45; 6,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,03</t>
+          <t>3,28; 7,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,58</t>
+          <t>2,02; 4,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,27</t>
+          <t>4,03; 7,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,38</t>
+          <t>1,89; 4,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,21</t>
+          <t>2,76; 5,7</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,46</t>
+          <t>1,99; 8,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,43</t>
+          <t>1,58; 6,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 15,27</t>
+          <t>6,27; 15,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 14,82</t>
+          <t>6,6; 14,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,04</t>
+          <t>2,93; 9,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,6</t>
+          <t>2,17; 5,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,44</t>
+          <t>4,87; 10,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,03</t>
+          <t>4,59; 9,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,14</t>
+          <t>1,47; 5,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,26</t>
+          <t>1,35; 3,04</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,19</t>
+          <t>0,72; 4,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,64</t>
+          <t>0,78; 4,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,38</t>
+          <t>0,75; 4,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,24</t>
+          <t>1,32; 4,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,55</t>
+          <t>1,82; 6,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,28</t>
+          <t>3,58; 9,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,11</t>
+          <t>2,67; 7,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,79</t>
+          <t>3,73; 7,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,56</t>
+          <t>1,61; 4,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,97</t>
+          <t>2,64; 6,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,31</t>
+          <t>2,21; 5,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,59</t>
+          <t>2,94; 5,28</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,07</t>
+          <t>2,62; 5,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,54</t>
+          <t>0,59; 2,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,59</t>
+          <t>0,75; 2,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,4</t>
+          <t>1,19; 3,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,55</t>
+          <t>2,54; 5,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,63</t>
+          <t>3,24; 6,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,24</t>
+          <t>2,09; 5,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,03</t>
+          <t>3,45; 6,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,2</t>
+          <t>2,86; 5,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,14</t>
+          <t>2,14; 4,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,48</t>
+          <t>1,71; 3,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,78</t>
+          <t>2,8; 4,47</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,87</t>
+          <t>2,93; 5,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,35</t>
+          <t>0,69; 2,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,7</t>
+          <t>0,1; 1,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,12</t>
+          <t>1,8; 3,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,83</t>
+          <t>4,9; 8,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,94</t>
+          <t>4,41; 7,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,36</t>
+          <t>2,55; 5,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,51</t>
+          <t>9,01; 12,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,72</t>
+          <t>4,35; 6,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,86</t>
+          <t>2,88; 4,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,12</t>
+          <t>1,46; 3,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,68</t>
+          <t>5,8; 7,88</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,5</t>
+          <t>2,4; 3,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,66</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,76</t>
+          <t>0,97; 1,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,26</t>
+          <t>1,49; 2,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,87</t>
+          <t>4,35; 5,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,67</t>
+          <t>5,04; 6,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,49</t>
+          <t>3,11; 4,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,87</t>
+          <t>4,89; 6,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,55; 4,53</t>
+          <t>3,54; 4,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,5</t>
+          <t>3,55; 4,45</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,02</t>
+          <t>2,23; 2,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 3,98</t>
+          <t>3,35; 4,08</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10363</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3642; 15327</t>
+          <t>3750; 15315</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1990; 13443</t>
+          <t>1959; 13488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1988; 12107</t>
+          <t>2015; 11799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3501</t>
+          <t>0; 2980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6244; 21321</t>
+          <t>6484; 20486</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5178; 19089</t>
+          <t>5109; 20852</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5668; 19051</t>
+          <t>5773; 20892</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5881; 14354</t>
+          <t>5995; 15293</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12854; 31016</t>
+          <t>12417; 29885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8919; 27462</t>
+          <t>8924; 25719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9629; 27288</t>
+          <t>9832; 27443</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6060; 16003</t>
+          <t>6545; 16421</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13280</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2035; 11335</t>
+          <t>1945; 10716</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7434; 26726</t>
+          <t>7422; 26176</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2891; 13881</t>
+          <t>3000; 13070</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>868; 9312</t>
+          <t>916; 9186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19562; 40162</t>
+          <t>20292; 40019</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18057; 37320</t>
+          <t>17892; 38281</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8886; 24401</t>
+          <t>8897; 25325</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5336; 15765</t>
+          <t>5625; 15938</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23620; 46728</t>
+          <t>24159; 45941</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29148; 56185</t>
+          <t>29859; 57974</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14789; 34514</t>
+          <t>14348; 33218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7496; 20378</t>
+          <t>7637; 21499</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21498</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>993; 10605</t>
+          <t>968; 9459</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1991; 11102</t>
+          <t>2001; 10769</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3348; 13270</t>
+          <t>3311; 12725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2622; 10538</t>
+          <t>2605; 10941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3182; 14474</t>
+          <t>3768; 14816</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11433; 30405</t>
+          <t>12808; 30920</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5777; 19630</t>
+          <t>5902; 20064</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10828; 22619</t>
+          <t>10817; 23138</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5829; 19646</t>
+          <t>6000; 20114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16293; 36782</t>
+          <t>16245; 36758</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11087; 27690</t>
+          <t>10917; 27796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15304; 30425</t>
+          <t>15259; 29563</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>31689</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2926; 13644</t>
+          <t>2890; 14303</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6618; 20724</t>
+          <t>6596; 21877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2538; 14209</t>
+          <t>2475; 13075</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5076; 18596</t>
+          <t>5343; 21754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9148; 24547</t>
+          <t>9301; 24274</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19967; 40321</t>
+          <t>19880; 40393</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9539; 25809</t>
+          <t>9485; 25792</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9181; 28652</t>
+          <t>13827; 31291</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14642; 33412</t>
+          <t>14715; 33523</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28765; 55354</t>
+          <t>30680; 54470</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13621; 33182</t>
+          <t>14293; 34797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19043; 41039</t>
+          <t>21936; 45318</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>9104</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4082; 17205</t>
+          <t>4049; 17164</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3444; 15789</t>
+          <t>3361; 14835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13481; 31703</t>
+          <t>13025; 31163</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13998; 32540</t>
+          <t>14499; 32784</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6426; 21953</t>
+          <t>6407; 21519</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4855; 11684</t>
+          <t>4939; 11993</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19823; 42914</t>
+          <t>19995; 42898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20926; 43337</t>
+          <t>19845; 40369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6598; 22082</t>
+          <t>6302; 21990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5554; 12627</t>
+          <t>5839; 13145</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21065</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1984; 11350</t>
+          <t>1943; 11560</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3023; 12706</t>
+          <t>2149; 12604</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1924; 11522</t>
+          <t>1967; 11472</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3785; 11422</t>
+          <t>3586; 11330</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5083; 18229</t>
+          <t>5066; 17977</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10141; 25891</t>
+          <t>9993; 25240</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7484; 22161</t>
+          <t>7306; 21210</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10039; 20034</t>
+          <t>9831; 20348</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9603; 25015</t>
+          <t>8850; 24501</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13537; 33011</t>
+          <t>14602; 34108</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10956; 28484</t>
+          <t>11828; 29547</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15663; 29463</t>
+          <t>15717; 28236</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>36737</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>52356</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16381; 37317</t>
+          <t>16095; 36494</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3974; 16856</t>
+          <t>3922; 16893</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4924; 17011</t>
+          <t>4947; 17942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7962; 21220</t>
+          <t>8577; 23988</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16037; 35428</t>
+          <t>16221; 35921</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23044; 46026</t>
+          <t>22512; 46963</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14782; 36252</t>
+          <t>14448; 34873</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13829; 42747</t>
+          <t>26599; 46460</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37853; 65183</t>
+          <t>35868; 65006</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29056; 56226</t>
+          <t>29058; 56457</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23185; 46949</t>
+          <t>23057; 45006</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25752; 55638</t>
+          <t>41792; 66605</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>21321</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>82609</t>
+          <t>88859</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>100985</t>
+          <t>110180</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22458; 43582</t>
+          <t>21769; 43265</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5300; 18296</t>
+          <t>5392; 18498</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>858; 13198</t>
+          <t>814; 11541</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6762; 29013</t>
+          <t>14339; 30867</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>39348; 69180</t>
+          <t>38398; 68565</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37324; 65205</t>
+          <t>36218; 64973</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20647; 44255</t>
+          <t>21079; 44762</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>70215; 103694</t>
+          <t>74800; 105581</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66258; 102548</t>
+          <t>66380; 103897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46988; 77709</t>
+          <t>46054; 77071</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>23474; 50069</t>
+          <t>23432; 48491</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>60170; 126196</t>
+          <t>94382; 128263</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>65800</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>203735</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>246942</t>
+          <t>269535</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>78300; 114764</t>
+          <t>78523; 115374</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>54702; 90999</t>
+          <t>56285; 91026</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33114; 59638</t>
+          <t>33086; 60175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45136; 78273</t>
+          <t>52578; 83495</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>146473; 198455</t>
+          <t>147081; 200905</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>177098; 236451</t>
+          <t>178549; 236700</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>111719; 159042</t>
+          <t>110235; 158867</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>153628; 214832</t>
+          <t>182405; 226977</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>236178; 301417</t>
+          <t>235431; 299774</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>246216; 313136</t>
+          <t>247370; 309906</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152690; 209726</t>
+          <t>154872; 206987</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>212623; 282968</t>
+          <t>242954; 296333</t>
         </is>
       </c>
     </row>
